--- a/artfynd/A 18748-2024 artfynd.xlsx
+++ b/artfynd/A 18748-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,6 +810,254 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118132008</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rotdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>333033</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6627549</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118131824</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rotdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333614</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6627593</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Brorson Edh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18748-2024 artfynd.xlsx
+++ b/artfynd/A 18748-2024 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>

--- a/artfynd/A 18748-2024 artfynd.xlsx
+++ b/artfynd/A 18748-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118122990</v>
+        <v>118131824</v>
       </c>
       <c r="B2" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,50 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rotdalen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333267</v>
+        <v>333614</v>
       </c>
       <c r="R2" t="n">
-        <v>6627628</v>
+        <v>6627593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,27 +767,17 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög upp när jag gick längs stigen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -813,19 +794,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118131824</v>
+        <v>118132008</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -865,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333614</v>
+        <v>333033</v>
       </c>
       <c r="R3" t="n">
-        <v>6627593</v>
+        <v>6627549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118132008</v>
+        <v>118201524</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,12 +941,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -985,17 +960,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rotdalen, Vrm</t>
+          <t>Påterud, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333033</v>
+        <v>333138</v>
       </c>
       <c r="R4" t="n">
-        <v>6627549</v>
+        <v>6627494</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,29 +994,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosök/hackmärken på liggande trädstam. Äldre spår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1049,15 +1019,148 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Monica Brandel Löved</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Monica Brandel Löved</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118122990</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rotdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>333267</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6627628</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög upp när jag gick längs stigen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Petter Brorson Edh</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Petter Brorson Edh</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
